--- a/samples/D_科目余额表.xlsx
+++ b/samples/D_科目余额表.xlsx
@@ -438,11 +438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -583,66 +583,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>银行存款</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>5870000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>18805000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>18055000</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>6620000</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>应收账款</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1680000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>38600000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>38350000</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
